--- a/main/ig/StructureDefinition-ror-questionnaire.xlsx
+++ b/main/ig/StructureDefinition-ror-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T15:54:27+00:00</t>
+    <t>2026-01-30T10:12:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-questionnaire.xlsx
+++ b/main/ig/StructureDefinition-ror-questionnaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:12:59+00:00</t>
+    <t>2026-03-09T13:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
